--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260715.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260715.xlsx
@@ -843,17 +843,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>28,150,000</t>
+          <t>25,514,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>25,514,000</t>
+          <t>28,150,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
